--- a/DATA/MODELADO/Diagnosticos/Exp04/recomendaciones_Exp04.xlsx
+++ b/DATA/MODELADO/Diagnosticos/Exp04/recomendaciones_Exp04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,26 +438,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>• El conjunto presenta desbalance de clases; utilizar técnicas de balanceo antes del entrenamiento.</t>
+          <t>• Incrementar la capacidad predictiva del modelo ajustando su arquitectura.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>• Comparar el desempeño del modelo LSTM con Random Forest, XGBoost y Redes Dense.</t>
+          <t>• Reducir el error absoluto revisando la selección de variables predictoras.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>• Evaluar el modelo utilizando validación cruzada temporal.</t>
+          <t>• Mejorar la precisión relativa mediante ajuste de hiperparámetros.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>• Comparar el desempeño del modelo LSTM con Random Forest, XGBoost y Redes Dense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>• Evaluar el modelo utilizando validación cruzada temporal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>• Documentar todos los experimentos para garantizar la reproducibilidad.</t>
         </is>
